--- a/stemma_tables.xlsx
+++ b/stemma_tables.xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="presence_sim" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="order_sim" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="orthography_sim" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="total_dist" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="total_similarity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="total_dist" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -608,7 +609,7 @@
         <v>0.1429</v>
       </c>
       <c r="M2" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.0752</v>
       </c>
       <c r="N2" t="n">
         <v>0.5931999999999999</v>
@@ -620,7 +621,7 @@
         <v>0.3824</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1279</v>
+        <v>0.131</v>
       </c>
       <c r="R2" t="n">
         <v>0.1064</v>
@@ -629,7 +630,7 @@
         <v>0.3077</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1325</v>
+        <v>0.1333</v>
       </c>
       <c r="U2" t="n">
         <v>0.0833</v>
@@ -696,7 +697,7 @@
         <v>0.1224</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0331</v>
+        <v>0.0328</v>
       </c>
       <c r="N3" t="n">
         <v>0.3276</v>
@@ -708,7 +709,7 @@
         <v>0.2623</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1111</v>
+        <v>0.1143</v>
       </c>
       <c r="R3" t="n">
         <v>0.129</v>
@@ -717,7 +718,7 @@
         <v>0.202</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0823</v>
+        <v>0.0828</v>
       </c>
       <c r="U3" t="n">
         <v>0.0482</v>
@@ -769,22 +770,22 @@
         <v>0.0968</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0988</v>
+        <v>0.1125</v>
       </c>
       <c r="I4" t="n">
         <v>0.0588</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0866</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1</v>
+        <v>0.1139</v>
       </c>
       <c r="L4" t="n">
         <v>0.1071</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0233</v>
+        <v>0.0231</v>
       </c>
       <c r="N4" t="n">
         <v>0.12</v>
@@ -796,16 +797,16 @@
         <v>0.1351</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.061</v>
+        <v>0.0625</v>
       </c>
       <c r="R4" t="n">
         <v>0.0769</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0862</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0788</v>
+        <v>0.0793</v>
       </c>
       <c r="U4" t="n">
         <v>0.0217</v>
@@ -814,7 +815,7 @@
         <v>0.0385</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0853</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="X4" t="n">
         <v>0.08699999999999999</v>
@@ -823,10 +824,10 @@
         <v>0.0808</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.0769</v>
+        <v>0.0853</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.1111</v>
+        <v>0.125</v>
       </c>
       <c r="AB4" t="n">
         <v>0.0345</v>
@@ -872,7 +873,7 @@
         <v>0.0571</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0094</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="N5" t="n">
         <v>0.0172</v>
@@ -884,7 +885,7 @@
         <v>0.0172</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.0164</v>
+        <v>0.0169</v>
       </c>
       <c r="R5" t="n">
         <v>0.1333</v>
@@ -893,7 +894,7 @@
         <v>0.0202</v>
       </c>
       <c r="T5" t="n">
-        <v>0.02</v>
+        <v>0.0201</v>
       </c>
       <c r="U5" t="n">
         <v>0.0455</v>
@@ -960,7 +961,7 @@
         <v>0.1188</v>
       </c>
       <c r="M6" t="n">
-        <v>0.064</v>
+        <v>0.0636</v>
       </c>
       <c r="N6" t="n">
         <v>0.1345</v>
@@ -972,7 +973,7 @@
         <v>0.09760000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1597</v>
+        <v>0.1624</v>
       </c>
       <c r="R6" t="n">
         <v>0.06900000000000001</v>
@@ -981,7 +982,7 @@
         <v>0.0994</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1393</v>
+        <v>0.14</v>
       </c>
       <c r="U6" t="n">
         <v>0.0584</v>
@@ -1033,22 +1034,22 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1736</v>
+        <v>0.1655</v>
       </c>
       <c r="I7" t="n">
         <v>0.2584</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2529</v>
+        <v>0.2457</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1915</v>
+        <v>0.1831</v>
       </c>
       <c r="L7" t="n">
         <v>0.1452</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1522</v>
+        <v>0.1514</v>
       </c>
       <c r="N7" t="n">
         <v>0.2239</v>
@@ -1057,28 +1058,28 @@
         <v>0.0796</v>
       </c>
       <c r="P7" t="n">
-        <v>0.1884</v>
+        <v>0.1799</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1438</v>
+        <v>0.162</v>
       </c>
       <c r="R7" t="n">
         <v>0.1091</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2047</v>
+        <v>0.1977</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2464</v>
+        <v>0.2476</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1299</v>
+        <v>0.1373</v>
       </c>
       <c r="V7" t="n">
         <v>0.2216</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2571</v>
+        <v>0.25</v>
       </c>
       <c r="X7" t="n">
         <v>0.1017</v>
@@ -1087,10 +1088,10 @@
         <v>0.3169</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.25</v>
+        <v>0.2429</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.1724</v>
+        <v>0.1644</v>
       </c>
       <c r="AB7" t="n">
         <v>0.0185</v>
@@ -1109,7 +1110,7 @@
         <v>0.2239</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0988</v>
+        <v>0.1125</v>
       </c>
       <c r="E8" t="n">
         <v>0.0323</v>
@@ -1118,13 +1119,13 @@
         <v>0.0853</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1736</v>
+        <v>0.1655</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1274</v>
+        <v>0.1203</v>
       </c>
       <c r="J8" t="n">
         <v>0.4492</v>
@@ -1136,7 +1137,7 @@
         <v>0.1176</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0784</v>
+        <v>0.0779</v>
       </c>
       <c r="N8" t="n">
         <v>0.3146</v>
@@ -1148,7 +1149,7 @@
         <v>0.3295</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.0926</v>
       </c>
       <c r="R8" t="n">
         <v>0.08699999999999999</v>
@@ -1157,13 +1158,13 @@
         <v>0.325</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1164</v>
+        <v>0.1111</v>
       </c>
       <c r="U8" t="n">
         <v>0.0672</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1126</v>
+        <v>0.1053</v>
       </c>
       <c r="W8" t="n">
         <v>0.4914</v>
@@ -1209,22 +1210,22 @@
         <v>0.2584</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1274</v>
+        <v>0.1203</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1832</v>
+        <v>0.1771</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1282</v>
+        <v>0.121</v>
       </c>
       <c r="L9" t="n">
         <v>0.08699999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2155</v>
+        <v>0.2143</v>
       </c>
       <c r="N9" t="n">
         <v>0.1544</v>
@@ -1233,28 +1234,28 @@
         <v>0.0484</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1097</v>
+        <v>0.1026</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1146</v>
+        <v>0.1382</v>
       </c>
       <c r="R9" t="n">
         <v>0.06560000000000001</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1568</v>
+        <v>0.1505</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4696</v>
+        <v>0.4722</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1447</v>
+        <v>0.1519</v>
       </c>
       <c r="V9" t="n">
         <v>0.4481</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1753</v>
+        <v>0.1692</v>
       </c>
       <c r="X9" t="n">
         <v>0.0698</v>
@@ -1263,10 +1264,10 @@
         <v>0.2829</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.1813</v>
+        <v>0.1753</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.1266</v>
+        <v>0.1195</v>
       </c>
       <c r="AB9" t="n">
         <v>0.0172</v>
@@ -1285,7 +1286,7 @@
         <v>0.1696</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0866</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="E10" t="n">
         <v>0.018</v>
@@ -1294,13 +1295,13 @@
         <v>0.0988</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2529</v>
+        <v>0.2457</v>
       </c>
       <c r="H10" t="n">
         <v>0.4492</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1832</v>
+        <v>0.1771</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1312,7 +1313,7 @@
         <v>0.1163</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1323</v>
+        <v>0.1316</v>
       </c>
       <c r="N10" t="n">
         <v>0.3833</v>
@@ -1324,7 +1325,7 @@
         <v>0.395</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0833</v>
+        <v>0.0844</v>
       </c>
       <c r="R10" t="n">
         <v>0.0598</v>
@@ -1333,13 +1334,13 @@
         <v>0.4545</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1818</v>
+        <v>0.1773</v>
       </c>
       <c r="U10" t="n">
         <v>0.0732</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1302</v>
+        <v>0.1244</v>
       </c>
       <c r="W10" t="n">
         <v>0.8048999999999999</v>
@@ -1373,7 +1374,7 @@
         <v>0.2462</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1</v>
+        <v>0.1139</v>
       </c>
       <c r="E11" t="n">
         <v>0.05</v>
@@ -1382,13 +1383,13 @@
         <v>0.0945</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1915</v>
+        <v>0.1831</v>
       </c>
       <c r="H11" t="n">
         <v>0.8905999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1282</v>
+        <v>0.121</v>
       </c>
       <c r="J11" t="n">
         <v>0.453</v>
@@ -1400,7 +1401,7 @@
         <v>0.119</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0789</v>
+        <v>0.0784</v>
       </c>
       <c r="N11" t="n">
         <v>0.3034</v>
@@ -1412,7 +1413,7 @@
         <v>0.3034</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.0917</v>
+        <v>0.0935</v>
       </c>
       <c r="R11" t="n">
         <v>0.1045</v>
@@ -1421,13 +1422,13 @@
         <v>0.339</v>
       </c>
       <c r="T11" t="n">
-        <v>0.123</v>
+        <v>0.1176</v>
       </c>
       <c r="U11" t="n">
         <v>0.0678</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1208</v>
+        <v>0.1133</v>
       </c>
       <c r="W11" t="n">
         <v>0.4957</v>
@@ -1488,7 +1489,7 @@
         <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0376</v>
+        <v>0.0373</v>
       </c>
       <c r="N12" t="n">
         <v>0.1688</v>
@@ -1500,7 +1501,7 @@
         <v>0.1538</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.1071</v>
+        <v>0.1098</v>
       </c>
       <c r="R12" t="n">
         <v>0.2973</v>
@@ -1509,7 +1510,7 @@
         <v>0.1282</v>
       </c>
       <c r="T12" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.0958</v>
       </c>
       <c r="U12" t="n">
         <v>0.0417</v>
@@ -1543,82 +1544,82 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.0752</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0331</v>
+        <v>0.0328</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0233</v>
+        <v>0.0231</v>
       </c>
       <c r="E13" t="n">
-        <v>0.0094</v>
+        <v>0.009299999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>0.064</v>
+        <v>0.0636</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1522</v>
+        <v>0.1514</v>
       </c>
       <c r="H13" t="n">
+        <v>0.0779</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.2143</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.1316</v>
+      </c>
+      <c r="K13" t="n">
         <v>0.0784</v>
       </c>
-      <c r="I13" t="n">
-        <v>0.2155</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.1323</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.0789</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.0376</v>
+        <v>0.0373</v>
       </c>
       <c r="M13" t="n">
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>0.0959</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0261</v>
+        <v>0.0259</v>
       </c>
       <c r="P13" t="n">
-        <v>0.0526</v>
+        <v>0.0523</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="R13" t="n">
-        <v>0.0351</v>
+        <v>0.0348</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1285</v>
+        <v>0.1278</v>
       </c>
       <c r="T13" t="n">
         <v>0.2212</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1409</v>
+        <v>0.1554</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1593</v>
+        <v>0.1585</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1077</v>
+        <v>0.1071</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0328</v>
+        <v>0.0325</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.1806</v>
+        <v>0.1795</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.1134</v>
+        <v>0.1128</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.0779</v>
+        <v>0.0774</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -1664,7 +1665,7 @@
         <v>0.1688</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0959</v>
+        <v>0.09520000000000001</v>
       </c>
       <c r="N14" t="n">
         <v>1</v>
@@ -1676,7 +1677,7 @@
         <v>0.4359</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.1616</v>
+        <v>0.1649</v>
       </c>
       <c r="R14" t="n">
         <v>0.1111</v>
@@ -1685,7 +1686,7 @@
         <v>0.3051</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1638</v>
+        <v>0.1648</v>
       </c>
       <c r="U14" t="n">
         <v>0.0796</v>
@@ -1752,7 +1753,7 @@
         <v>0.2973</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0261</v>
+        <v>0.0259</v>
       </c>
       <c r="N15" t="n">
         <v>0.09379999999999999</v>
@@ -1764,7 +1765,7 @@
         <v>0.0448</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0429</v>
+        <v>0.0441</v>
       </c>
       <c r="R15" t="n">
         <v>0.4</v>
@@ -1773,7 +1774,7 @@
         <v>0.0566</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0314</v>
+        <v>0.0316</v>
       </c>
       <c r="U15" t="n">
         <v>0.0526</v>
@@ -1822,13 +1823,13 @@
         <v>0.09760000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1884</v>
+        <v>0.1799</v>
       </c>
       <c r="H16" t="n">
         <v>0.3295</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1097</v>
+        <v>0.1026</v>
       </c>
       <c r="J16" t="n">
         <v>0.395</v>
@@ -1840,7 +1841,7 @@
         <v>0.1538</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0526</v>
+        <v>0.0523</v>
       </c>
       <c r="N16" t="n">
         <v>0.4359</v>
@@ -1852,7 +1853,7 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.0849</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="R16" t="n">
         <v>0.0606</v>
@@ -1861,13 +1862,13 @@
         <v>0.3874</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1444</v>
+        <v>0.1389</v>
       </c>
       <c r="U16" t="n">
         <v>0.0517</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1014</v>
+        <v>0.094</v>
       </c>
       <c r="W16" t="n">
         <v>0.3884</v>
@@ -1895,85 +1896,85 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.1279</v>
+        <v>0.131</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1111</v>
+        <v>0.1143</v>
       </c>
       <c r="D17" t="n">
-        <v>0.061</v>
+        <v>0.0625</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0164</v>
+        <v>0.0169</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1597</v>
+        <v>0.1624</v>
       </c>
       <c r="G17" t="n">
-        <v>0.1438</v>
+        <v>0.162</v>
       </c>
       <c r="H17" t="n">
-        <v>0.09089999999999999</v>
+        <v>0.0926</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1146</v>
+        <v>0.1382</v>
       </c>
       <c r="J17" t="n">
-        <v>0.0833</v>
+        <v>0.0844</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0917</v>
+        <v>0.0935</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1071</v>
+        <v>0.1098</v>
       </c>
       <c r="M17" t="n">
-        <v>0.07240000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1616</v>
+        <v>0.1649</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0429</v>
+        <v>0.0441</v>
       </c>
       <c r="P17" t="n">
-        <v>0.0849</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="Q17" t="n">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0.0896</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0979</v>
+        <v>0.0993</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1176</v>
+        <v>0.1319</v>
       </c>
       <c r="U17" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0789</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1448</v>
+        <v>0.1631</v>
       </c>
       <c r="W17" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.0974</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1096</v>
+        <v>0.1127</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.1405</v>
+        <v>0.1525</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.1032</v>
+        <v>0.1046</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.0804</v>
+        <v>0.0818</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.0167</v>
+        <v>0.0172</v>
       </c>
     </row>
     <row r="18">
@@ -2016,7 +2017,7 @@
         <v>0.2973</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0351</v>
+        <v>0.0348</v>
       </c>
       <c r="N18" t="n">
         <v>0.1111</v>
@@ -2028,7 +2029,7 @@
         <v>0.0606</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.0896</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
@@ -2037,7 +2038,7 @@
         <v>0.0769</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0513</v>
+        <v>0.0516</v>
       </c>
       <c r="U18" t="n">
         <v>0.0526</v>
@@ -2077,7 +2078,7 @@
         <v>0.202</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0862</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="E19" t="n">
         <v>0.0202</v>
@@ -2086,13 +2087,13 @@
         <v>0.0994</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2047</v>
+        <v>0.1977</v>
       </c>
       <c r="H19" t="n">
         <v>0.325</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1568</v>
+        <v>0.1505</v>
       </c>
       <c r="J19" t="n">
         <v>0.4545</v>
@@ -2104,7 +2105,7 @@
         <v>0.1282</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1285</v>
+        <v>0.1278</v>
       </c>
       <c r="N19" t="n">
         <v>0.3051</v>
@@ -2116,7 +2117,7 @@
         <v>0.3874</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.0979</v>
+        <v>0.0993</v>
       </c>
       <c r="R19" t="n">
         <v>0.0769</v>
@@ -2125,13 +2126,13 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>0.181</v>
+        <v>0.1762</v>
       </c>
       <c r="U19" t="n">
         <v>0.0513</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1648</v>
+        <v>0.1582</v>
       </c>
       <c r="W19" t="n">
         <v>0.4789</v>
@@ -2159,85 +2160,85 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.1325</v>
+        <v>0.1333</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0823</v>
+        <v>0.0828</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0788</v>
+        <v>0.0793</v>
       </c>
       <c r="E20" t="n">
-        <v>0.02</v>
+        <v>0.0201</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1393</v>
+        <v>0.14</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2464</v>
+        <v>0.2476</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1164</v>
+        <v>0.1111</v>
       </c>
       <c r="I20" t="n">
-        <v>0.4696</v>
+        <v>0.4722</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1818</v>
+        <v>0.1773</v>
       </c>
       <c r="K20" t="n">
-        <v>0.123</v>
+        <v>0.1176</v>
       </c>
       <c r="L20" t="n">
-        <v>0.09520000000000001</v>
+        <v>0.0958</v>
       </c>
       <c r="M20" t="n">
         <v>0.2212</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1638</v>
+        <v>0.1648</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0314</v>
+        <v>0.0316</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1444</v>
+        <v>0.1389</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.1176</v>
+        <v>0.1319</v>
       </c>
       <c r="R20" t="n">
-        <v>0.0513</v>
+        <v>0.0516</v>
       </c>
       <c r="S20" t="n">
-        <v>0.181</v>
+        <v>0.1762</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1429</v>
+        <v>0.1497</v>
       </c>
       <c r="V20" t="n">
-        <v>0.4121</v>
+        <v>0.4144</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2018</v>
+        <v>0.1972</v>
       </c>
       <c r="X20" t="n">
-        <v>0.075</v>
+        <v>0.0755</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.2865</v>
+        <v>0.2881</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.2018</v>
+        <v>0.1972</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.1217</v>
+        <v>0.1164</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.0133</v>
+        <v>0.0134</v>
       </c>
     </row>
     <row r="21">
@@ -2262,13 +2263,13 @@
         <v>0.0584</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1299</v>
+        <v>0.1373</v>
       </c>
       <c r="H21" t="n">
         <v>0.0672</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1447</v>
+        <v>0.1519</v>
       </c>
       <c r="J21" t="n">
         <v>0.0732</v>
@@ -2280,7 +2281,7 @@
         <v>0.0417</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1409</v>
+        <v>0.1554</v>
       </c>
       <c r="N21" t="n">
         <v>0.0796</v>
@@ -2292,7 +2293,7 @@
         <v>0.0517</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.0789</v>
       </c>
       <c r="R21" t="n">
         <v>0.0526</v>
@@ -2301,13 +2302,13 @@
         <v>0.0513</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1429</v>
+        <v>0.1497</v>
       </c>
       <c r="U21" t="n">
         <v>1</v>
       </c>
       <c r="V21" t="n">
-        <v>0.1234</v>
+        <v>0.1307</v>
       </c>
       <c r="W21" t="n">
         <v>0.0659</v>
@@ -2316,7 +2317,7 @@
         <v>0.0476</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.1508</v>
+        <v>0.1694</v>
       </c>
       <c r="Z21" t="n">
         <v>0.0659</v>
@@ -2353,22 +2354,22 @@
         <v>0.2216</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1126</v>
+        <v>0.1053</v>
       </c>
       <c r="I22" t="n">
         <v>0.4481</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1302</v>
+        <v>0.1244</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1208</v>
+        <v>0.1133</v>
       </c>
       <c r="L22" t="n">
         <v>0.119</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1593</v>
+        <v>0.1585</v>
       </c>
       <c r="N22" t="n">
         <v>0.1164</v>
@@ -2377,28 +2378,28 @@
         <v>0.0522</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1014</v>
+        <v>0.094</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1448</v>
+        <v>0.1631</v>
       </c>
       <c r="R22" t="n">
         <v>0.0708</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1648</v>
+        <v>0.1582</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4121</v>
+        <v>0.4144</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1234</v>
+        <v>0.1307</v>
       </c>
       <c r="V22" t="n">
         <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>0.1526</v>
+        <v>0.1466</v>
       </c>
       <c r="X22" t="n">
         <v>0.08400000000000001</v>
@@ -2407,10 +2408,10 @@
         <v>0.2917</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.1526</v>
+        <v>0.1466</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.1118</v>
+        <v>0.1046</v>
       </c>
       <c r="AB22" t="n">
         <v>0.0187</v>
@@ -2429,7 +2430,7 @@
         <v>0.177</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0853</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="E23" t="n">
         <v>0.0177</v>
@@ -2438,13 +2439,13 @@
         <v>0.104</v>
       </c>
       <c r="G23" t="n">
-        <v>0.2571</v>
+        <v>0.25</v>
       </c>
       <c r="H23" t="n">
         <v>0.4914</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1753</v>
+        <v>0.1692</v>
       </c>
       <c r="J23" t="n">
         <v>0.8048999999999999</v>
@@ -2456,7 +2457,7 @@
         <v>0.1318</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1077</v>
+        <v>0.1071</v>
       </c>
       <c r="N23" t="n">
         <v>0.3884</v>
@@ -2468,7 +2469,7 @@
         <v>0.3884</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.0974</v>
       </c>
       <c r="R23" t="n">
         <v>0.0588</v>
@@ -2477,13 +2478,13 @@
         <v>0.4789</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2018</v>
+        <v>0.1972</v>
       </c>
       <c r="U23" t="n">
         <v>0.0659</v>
       </c>
       <c r="V23" t="n">
-        <v>0.1526</v>
+        <v>0.1466</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
@@ -2544,7 +2545,7 @@
         <v>0.1429</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0328</v>
+        <v>0.0325</v>
       </c>
       <c r="N24" t="n">
         <v>0.322</v>
@@ -2556,7 +2557,7 @@
         <v>0.2787</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1096</v>
+        <v>0.1127</v>
       </c>
       <c r="R24" t="n">
         <v>0.125</v>
@@ -2565,7 +2566,7 @@
         <v>0.2</v>
       </c>
       <c r="T24" t="n">
-        <v>0.075</v>
+        <v>0.0755</v>
       </c>
       <c r="U24" t="n">
         <v>0.0476</v>
@@ -2632,7 +2633,7 @@
         <v>0.1649</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1806</v>
+        <v>0.1795</v>
       </c>
       <c r="N25" t="n">
         <v>0.2162</v>
@@ -2644,7 +2645,7 @@
         <v>0.1345</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.1405</v>
+        <v>0.1525</v>
       </c>
       <c r="R25" t="n">
         <v>0.1071</v>
@@ -2653,10 +2654,10 @@
         <v>0.1645</v>
       </c>
       <c r="T25" t="n">
-        <v>0.2865</v>
+        <v>0.2881</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1508</v>
+        <v>0.1694</v>
       </c>
       <c r="V25" t="n">
         <v>0.2917</v>
@@ -2693,7 +2694,7 @@
         <v>0.1667</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0769</v>
+        <v>0.0853</v>
       </c>
       <c r="E26" t="n">
         <v>0.0177</v>
@@ -2702,13 +2703,13 @@
         <v>0.117</v>
       </c>
       <c r="G26" t="n">
-        <v>0.25</v>
+        <v>0.2429</v>
       </c>
       <c r="H26" t="n">
         <v>0.4298</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1813</v>
+        <v>0.1753</v>
       </c>
       <c r="J26" t="n">
         <v>0.7619</v>
@@ -2720,7 +2721,7 @@
         <v>0.1231</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1134</v>
+        <v>0.1128</v>
       </c>
       <c r="N26" t="n">
         <v>0.377</v>
@@ -2732,7 +2733,7 @@
         <v>0.3659</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.1032</v>
+        <v>0.1046</v>
       </c>
       <c r="R26" t="n">
         <v>0.0588</v>
@@ -2741,13 +2742,13 @@
         <v>0.4286</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2018</v>
+        <v>0.1972</v>
       </c>
       <c r="U26" t="n">
         <v>0.0659</v>
       </c>
       <c r="V26" t="n">
-        <v>0.1526</v>
+        <v>0.1466</v>
       </c>
       <c r="W26" t="n">
         <v>0.7778</v>
@@ -2781,7 +2782,7 @@
         <v>0.2206</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1111</v>
+        <v>0.125</v>
       </c>
       <c r="E27" t="n">
         <v>0.0484</v>
@@ -2790,13 +2791,13 @@
         <v>0.093</v>
       </c>
       <c r="G27" t="n">
-        <v>0.1724</v>
+        <v>0.1644</v>
       </c>
       <c r="H27" t="n">
         <v>0.7826</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1266</v>
+        <v>0.1195</v>
       </c>
       <c r="J27" t="n">
         <v>0.4576</v>
@@ -2808,7 +2809,7 @@
         <v>0.1294</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0779</v>
+        <v>0.0774</v>
       </c>
       <c r="N27" t="n">
         <v>0.3111</v>
@@ -2820,7 +2821,7 @@
         <v>0.3563</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.0804</v>
+        <v>0.0818</v>
       </c>
       <c r="R27" t="n">
         <v>0.1176</v>
@@ -2829,13 +2830,13 @@
         <v>0.3333</v>
       </c>
       <c r="T27" t="n">
-        <v>0.1217</v>
+        <v>0.1164</v>
       </c>
       <c r="U27" t="n">
         <v>0.0667</v>
       </c>
       <c r="V27" t="n">
-        <v>0.1118</v>
+        <v>0.1046</v>
       </c>
       <c r="W27" t="n">
         <v>0.4872</v>
@@ -2908,7 +2909,7 @@
         <v>0.0175</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.0167</v>
+        <v>0.0172</v>
       </c>
       <c r="R28" t="n">
         <v>0.1429</v>
@@ -2917,7 +2918,7 @@
         <v>0.0101</v>
       </c>
       <c r="T28" t="n">
-        <v>0.0133</v>
+        <v>0.0134</v>
       </c>
       <c r="U28" t="n">
         <v>0.0303</v>
@@ -3296,16 +3297,16 @@
         <v>0.5385</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6667</v>
+        <v>0.6</v>
       </c>
       <c r="I4" t="n">
         <v>0.4444</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5833</v>
+        <v>0.5385</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6667</v>
+        <v>0.6</v>
       </c>
       <c r="L4" t="n">
         <v>0.5714</v>
@@ -3329,7 +3330,7 @@
         <v>0.5</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5455</v>
+        <v>0.5833</v>
       </c>
       <c r="T4" t="n">
         <v>0.5</v>
@@ -3341,7 +3342,7 @@
         <v>0.3333</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4167</v>
+        <v>0.3846</v>
       </c>
       <c r="X4" t="n">
         <v>0.6</v>
@@ -3350,10 +3351,10 @@
         <v>0.6667</v>
       </c>
       <c r="Z4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AA4" t="n">
         <v>0.5455</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0.6</v>
       </c>
       <c r="AB4" t="n">
         <v>1</v>
@@ -3560,16 +3561,16 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5</v>
+        <v>0.5185</v>
       </c>
       <c r="I7" t="n">
         <v>0.7</v>
       </c>
       <c r="J7" t="n">
-        <v>0.375</v>
+        <v>0.383</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4667</v>
+        <v>0.4828</v>
       </c>
       <c r="L7" t="n">
         <v>0.5789</v>
@@ -3584,28 +3585,28 @@
         <v>0.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4231</v>
+        <v>0.44</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5652</v>
+        <v>0.6</v>
       </c>
       <c r="R7" t="n">
         <v>0.5385</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3684</v>
+        <v>0.3784</v>
       </c>
       <c r="T7" t="n">
         <v>0.7091</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6667</v>
+        <v>0.6818</v>
       </c>
       <c r="V7" t="n">
         <v>0.6744</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3333</v>
+        <v>0.3404</v>
       </c>
       <c r="X7" t="n">
         <v>0.6667</v>
@@ -3614,10 +3615,10 @@
         <v>0.6327</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.3404</v>
+        <v>0.3478</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="AB7" t="n">
         <v>1</v>
@@ -3636,7 +3637,7 @@
         <v>0.9333</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6667</v>
+        <v>0.6</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
@@ -3645,13 +3646,13 @@
         <v>0.6364</v>
       </c>
       <c r="G8" t="n">
+        <v>0.5185</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
         <v>0.5</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.4762</v>
       </c>
       <c r="J8" t="n">
         <v>0.8793</v>
@@ -3663,7 +3664,7 @@
         <v>0.6364</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4</v>
+        <v>0.4286</v>
       </c>
       <c r="N8" t="n">
         <v>0.8276</v>
@@ -3684,13 +3685,13 @@
         <v>0.619</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4167</v>
+        <v>0.4348</v>
       </c>
       <c r="U8" t="n">
         <v>0.625</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3333</v>
+        <v>0.2941</v>
       </c>
       <c r="W8" t="n">
         <v>0.9</v>
@@ -3736,22 +3737,22 @@
         <v>0.7</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4762</v>
+        <v>0.5</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2821</v>
+        <v>0.2895</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5238</v>
+        <v>0.55</v>
       </c>
       <c r="L9" t="n">
         <v>0.6923</v>
       </c>
       <c r="M9" t="n">
-        <v>0.619</v>
+        <v>0.6341</v>
       </c>
       <c r="N9" t="n">
         <v>0.48</v>
@@ -3760,28 +3761,28 @@
         <v>0.8571</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6111</v>
+        <v>0.6471</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.7368</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="R9" t="n">
         <v>0.7778</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5</v>
+        <v>0.5161</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8539</v>
+        <v>0.8444</v>
       </c>
       <c r="U9" t="n">
-        <v>0.875</v>
+        <v>0.88</v>
       </c>
       <c r="V9" t="n">
         <v>0.9</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2703</v>
+        <v>0.2778</v>
       </c>
       <c r="X9" t="n">
         <v>0.7</v>
@@ -3790,10 +3791,10 @@
         <v>0.75</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.275</v>
+        <v>0.2821</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.5455</v>
+        <v>0.5714</v>
       </c>
       <c r="AB9" t="n">
         <v>0.6667</v>
@@ -3812,7 +3813,7 @@
         <v>0.9</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5833</v>
+        <v>0.5385</v>
       </c>
       <c r="E10" t="n">
         <v>0.6667</v>
@@ -3821,13 +3822,13 @@
         <v>0.4444</v>
       </c>
       <c r="G10" t="n">
-        <v>0.375</v>
+        <v>0.383</v>
       </c>
       <c r="H10" t="n">
         <v>0.8793</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2821</v>
+        <v>0.2895</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -3839,7 +3840,7 @@
         <v>0.4706</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2414</v>
+        <v>0.25</v>
       </c>
       <c r="N10" t="n">
         <v>0.7755</v>
@@ -3860,13 +3861,13 @@
         <v>0.6</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2955</v>
+        <v>0.3023</v>
       </c>
       <c r="U10" t="n">
         <v>0.3846</v>
       </c>
       <c r="V10" t="n">
-        <v>0.2414</v>
+        <v>0.25</v>
       </c>
       <c r="W10" t="n">
         <v>0.9519</v>
@@ -3900,7 +3901,7 @@
         <v>0.9375</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6667</v>
+        <v>0.6</v>
       </c>
       <c r="E11" t="n">
         <v>0.5</v>
@@ -3909,13 +3910,13 @@
         <v>0.6667</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4667</v>
+        <v>0.4828</v>
       </c>
       <c r="H11" t="n">
         <v>0.9828</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5238</v>
+        <v>0.55</v>
       </c>
       <c r="J11" t="n">
         <v>0.9137999999999999</v>
@@ -3927,7 +3928,7 @@
         <v>0.6364</v>
       </c>
       <c r="M11" t="n">
-        <v>0.4</v>
+        <v>0.4286</v>
       </c>
       <c r="N11" t="n">
         <v>0.8214</v>
@@ -3948,13 +3949,13 @@
         <v>0.6047</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4</v>
+        <v>0.4167</v>
       </c>
       <c r="U11" t="n">
         <v>0.5556</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3158</v>
+        <v>0.2778</v>
       </c>
       <c r="W11" t="n">
         <v>0.9333</v>
@@ -4088,16 +4089,16 @@
         <v>0.6333</v>
       </c>
       <c r="H13" t="n">
-        <v>0.4</v>
+        <v>0.4286</v>
       </c>
       <c r="I13" t="n">
-        <v>0.619</v>
+        <v>0.6341</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2414</v>
+        <v>0.25</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4</v>
+        <v>0.4286</v>
       </c>
       <c r="L13" t="n">
         <v>0.8</v>
@@ -4112,10 +4113,10 @@
         <v>1</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6667</v>
+        <v>0.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.8333</v>
+        <v>0.8462</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
@@ -4124,16 +4125,16 @@
         <v>0.3077</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6327</v>
+        <v>0.6458</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6818</v>
+        <v>0.6667</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5806</v>
+        <v>0.6</v>
       </c>
       <c r="W13" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="X13" t="n">
         <v>0.4</v>
@@ -4145,7 +4146,7 @@
         <v>0.28</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.4</v>
+        <v>0.4286</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -4349,13 +4350,13 @@
         <v>0.3846</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4231</v>
+        <v>0.44</v>
       </c>
       <c r="H16" t="n">
         <v>0.8621</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6111</v>
+        <v>0.6471</v>
       </c>
       <c r="J16" t="n">
         <v>0.9592000000000001</v>
@@ -4367,7 +4368,7 @@
         <v>0.4615</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6667</v>
+        <v>0.75</v>
       </c>
       <c r="N16" t="n">
         <v>0.7778</v>
@@ -4388,13 +4389,13 @@
         <v>0.7391</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4643</v>
+        <v>0.4815</v>
       </c>
       <c r="U16" t="n">
         <v>0.6667</v>
       </c>
       <c r="V16" t="n">
-        <v>0.4375</v>
+        <v>0.4667</v>
       </c>
       <c r="W16" t="n">
         <v>0.8776</v>
@@ -4437,13 +4438,13 @@
         <v>0.3684</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5652</v>
+        <v>0.6</v>
       </c>
       <c r="H17" t="n">
         <v>0.6</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7368</v>
+        <v>0.7272999999999999</v>
       </c>
       <c r="J17" t="n">
         <v>0.5385</v>
@@ -4455,7 +4456,7 @@
         <v>0.6</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8333</v>
+        <v>0.8462</v>
       </c>
       <c r="N17" t="n">
         <v>0.5</v>
@@ -4476,13 +4477,13 @@
         <v>0.5</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.5385</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6364</v>
+        <v>0.7</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6364</v>
+        <v>0.6667</v>
       </c>
       <c r="W17" t="n">
         <v>0.4</v>
@@ -4491,7 +4492,7 @@
         <v>0.6667</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.7059</v>
+        <v>0.7222</v>
       </c>
       <c r="Z17" t="n">
         <v>0.4118</v>
@@ -4604,7 +4605,7 @@
         <v>0.7619</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5455</v>
+        <v>0.5833</v>
       </c>
       <c r="E19" t="n">
         <v>0.5</v>
@@ -4613,13 +4614,13 @@
         <v>0.5294</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3684</v>
+        <v>0.3784</v>
       </c>
       <c r="H19" t="n">
         <v>0.619</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>0.5161</v>
       </c>
       <c r="J19" t="n">
         <v>0.6</v>
@@ -4652,13 +4653,13 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3571</v>
+        <v>0.3659</v>
       </c>
       <c r="U19" t="n">
         <v>0.6667</v>
       </c>
       <c r="V19" t="n">
-        <v>0.4516</v>
+        <v>0.4333</v>
       </c>
       <c r="W19" t="n">
         <v>0.6027</v>
@@ -4704,22 +4705,22 @@
         <v>0.7091</v>
       </c>
       <c r="H20" t="n">
+        <v>0.4348</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8444</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="K20" t="n">
         <v>0.4167</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.8539</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.2955</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0.4</v>
       </c>
       <c r="L20" t="n">
         <v>0.6471</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6327</v>
+        <v>0.6458</v>
       </c>
       <c r="N20" t="n">
         <v>0.3548</v>
@@ -4728,28 +4729,28 @@
         <v>0.8333</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4643</v>
+        <v>0.4815</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.5217000000000001</v>
+        <v>0.5385</v>
       </c>
       <c r="R20" t="n">
         <v>0.7778</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3571</v>
+        <v>0.3659</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0.75</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>0.825</v>
+        <v>0.8148</v>
       </c>
       <c r="W20" t="n">
-        <v>0.25</v>
+        <v>0.2553</v>
       </c>
       <c r="X20" t="n">
         <v>0.6153999999999999</v>
@@ -4758,10 +4759,10 @@
         <v>0.6667</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.24</v>
+        <v>0.2449</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.44</v>
+        <v>0.4583</v>
       </c>
       <c r="AB20" t="n">
         <v>0.6667</v>
@@ -4789,13 +4790,13 @@
         <v>0.6667</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6667</v>
+        <v>0.6818</v>
       </c>
       <c r="H21" t="n">
         <v>0.625</v>
       </c>
       <c r="I21" t="n">
-        <v>0.875</v>
+        <v>0.88</v>
       </c>
       <c r="J21" t="n">
         <v>0.3846</v>
@@ -4807,7 +4808,7 @@
         <v>0.8</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6818</v>
+        <v>0.6667</v>
       </c>
       <c r="N21" t="n">
         <v>0.5556</v>
@@ -4819,7 +4820,7 @@
         <v>0.6667</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.6364</v>
+        <v>0.7</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
@@ -4828,13 +4829,13 @@
         <v>0.6667</v>
       </c>
       <c r="T21" t="n">
-        <v>0.75</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="U21" t="n">
         <v>1</v>
       </c>
       <c r="V21" t="n">
-        <v>0.7</v>
+        <v>0.7143</v>
       </c>
       <c r="W21" t="n">
         <v>0.4167</v>
@@ -4843,7 +4844,7 @@
         <v>0.75</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.8</v>
+        <v>0.8182</v>
       </c>
       <c r="Z21" t="n">
         <v>0.4167</v>
@@ -4880,22 +4881,22 @@
         <v>0.6744</v>
       </c>
       <c r="H22" t="n">
-        <v>0.3333</v>
+        <v>0.2941</v>
       </c>
       <c r="I22" t="n">
         <v>0.9</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2414</v>
+        <v>0.25</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3158</v>
+        <v>0.2778</v>
       </c>
       <c r="L22" t="n">
         <v>0.6875</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5806</v>
+        <v>0.6</v>
       </c>
       <c r="N22" t="n">
         <v>0.3333</v>
@@ -4904,28 +4905,28 @@
         <v>0.8571</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4375</v>
+        <v>0.4667</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.6364</v>
+        <v>0.6667</v>
       </c>
       <c r="R22" t="n">
         <v>0.7778</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4516</v>
+        <v>0.4333</v>
       </c>
       <c r="T22" t="n">
-        <v>0.825</v>
+        <v>0.8148</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7</v>
+        <v>0.7143</v>
       </c>
       <c r="V22" t="n">
         <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>0.25</v>
+        <v>0.2581</v>
       </c>
       <c r="X22" t="n">
         <v>0.4545</v>
@@ -4934,10 +4935,10 @@
         <v>0.6279</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.2647</v>
+        <v>0.2727</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.3684</v>
+        <v>0.3333</v>
       </c>
       <c r="AB22" t="n">
         <v>0.6667</v>
@@ -4956,7 +4957,7 @@
         <v>0.8571</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4167</v>
+        <v>0.3846</v>
       </c>
       <c r="E23" t="n">
         <v>0.6667</v>
@@ -4965,13 +4966,13 @@
         <v>0.4737</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3333</v>
+        <v>0.3404</v>
       </c>
       <c r="H23" t="n">
         <v>0.9</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2703</v>
+        <v>0.2778</v>
       </c>
       <c r="J23" t="n">
         <v>0.9519</v>
@@ -4983,7 +4984,7 @@
         <v>0.4444</v>
       </c>
       <c r="M23" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="N23" t="n">
         <v>0.8367</v>
@@ -5004,13 +5005,13 @@
         <v>0.6027</v>
       </c>
       <c r="T23" t="n">
-        <v>0.25</v>
+        <v>0.2553</v>
       </c>
       <c r="U23" t="n">
         <v>0.4167</v>
       </c>
       <c r="V23" t="n">
-        <v>0.25</v>
+        <v>0.2581</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
@@ -5171,7 +5172,7 @@
         <v>0.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.7059</v>
+        <v>0.7222</v>
       </c>
       <c r="R25" t="n">
         <v>0.6667</v>
@@ -5183,7 +5184,7 @@
         <v>0.6667</v>
       </c>
       <c r="U25" t="n">
-        <v>0.8</v>
+        <v>0.8182</v>
       </c>
       <c r="V25" t="n">
         <v>0.6279</v>
@@ -5220,7 +5221,7 @@
         <v>0.8571</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5455</v>
+        <v>0.5</v>
       </c>
       <c r="E26" t="n">
         <v>0.6667</v>
@@ -5229,13 +5230,13 @@
         <v>0.4545</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3404</v>
+        <v>0.3478</v>
       </c>
       <c r="H26" t="n">
         <v>0.8793</v>
       </c>
       <c r="I26" t="n">
-        <v>0.275</v>
+        <v>0.2821</v>
       </c>
       <c r="J26" t="n">
         <v>0.9406</v>
@@ -5268,13 +5269,13 @@
         <v>0.6471</v>
       </c>
       <c r="T26" t="n">
-        <v>0.24</v>
+        <v>0.2449</v>
       </c>
       <c r="U26" t="n">
         <v>0.4167</v>
       </c>
       <c r="V26" t="n">
-        <v>0.2647</v>
+        <v>0.2727</v>
       </c>
       <c r="W26" t="n">
         <v>0.9327</v>
@@ -5308,7 +5309,7 @@
         <v>0.8125</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6</v>
+        <v>0.5455</v>
       </c>
       <c r="E27" t="n">
         <v>0.4</v>
@@ -5317,13 +5318,13 @@
         <v>0.6153999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="H27" t="n">
         <v>0.9286</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5455</v>
+        <v>0.5714</v>
       </c>
       <c r="J27" t="n">
         <v>0.8621</v>
@@ -5335,7 +5336,7 @@
         <v>0.6667</v>
       </c>
       <c r="M27" t="n">
-        <v>0.4</v>
+        <v>0.4286</v>
       </c>
       <c r="N27" t="n">
         <v>0.7586000000000001</v>
@@ -5356,13 +5357,13 @@
         <v>0.5714</v>
       </c>
       <c r="T27" t="n">
-        <v>0.44</v>
+        <v>0.4583</v>
       </c>
       <c r="U27" t="n">
         <v>0.5</v>
       </c>
       <c r="V27" t="n">
-        <v>0.3684</v>
+        <v>0.3333</v>
       </c>
       <c r="W27" t="n">
         <v>0.8643999999999999</v>
@@ -5823,16 +5824,16 @@
         <v>0.5417</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6875</v>
+        <v>0.6111</v>
       </c>
       <c r="I4" t="n">
         <v>0.6875</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5455</v>
+        <v>0.5</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6875</v>
+        <v>0.6111</v>
       </c>
       <c r="L4" t="n">
         <v>0.5833</v>
@@ -5856,7 +5857,7 @@
         <v>0.3333</v>
       </c>
       <c r="S4" t="n">
-        <v>0.65</v>
+        <v>0.5909</v>
       </c>
       <c r="T4" t="n">
         <v>0.7308</v>
@@ -5868,7 +5869,7 @@
         <v>0.4</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5909</v>
+        <v>0.5417</v>
       </c>
       <c r="X4" t="n">
         <v>0.625</v>
@@ -5877,10 +5878,10 @@
         <v>0.625</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.35</v>
+        <v>0.3182</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -6087,16 +6088,16 @@
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7</v>
+        <v>0.6875</v>
       </c>
       <c r="I7" t="n">
         <v>0.7609</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6705</v>
+        <v>0.6627999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6852</v>
+        <v>0.6731</v>
       </c>
       <c r="L7" t="n">
         <v>0.6111</v>
@@ -6111,28 +6112,28 @@
         <v>0.7778</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5385</v>
+        <v>0.52</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5714</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="R7" t="n">
         <v>0.6667</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6857</v>
+        <v>0.6765</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7255</v>
+        <v>0.7157</v>
       </c>
       <c r="U7" t="n">
-        <v>0.675</v>
+        <v>0.5952</v>
       </c>
       <c r="V7" t="n">
         <v>0.859</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7</v>
+        <v>0.6932</v>
       </c>
       <c r="X7" t="n">
         <v>1</v>
@@ -6141,10 +6142,10 @@
         <v>0.8333</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.6932</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.68</v>
+        <v>0.6667</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -6163,7 +6164,7 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6875</v>
+        <v>0.6111</v>
       </c>
       <c r="E8" t="n">
         <v>0.5</v>
@@ -6172,13 +6173,13 @@
         <v>0.8182</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7</v>
+        <v>0.6875</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.475</v>
+        <v>0.4474</v>
       </c>
       <c r="J8" t="n">
         <v>0.9056999999999999</v>
@@ -6211,13 +6212,13 @@
         <v>0.8718</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="U8" t="n">
         <v>0.875</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7647</v>
+        <v>0.75</v>
       </c>
       <c r="W8" t="n">
         <v>0.9560999999999999</v>
@@ -6263,16 +6264,16 @@
         <v>0.7609</v>
       </c>
       <c r="H9" t="n">
-        <v>0.475</v>
+        <v>0.4474</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7143</v>
+        <v>0.7059</v>
       </c>
       <c r="K9" t="n">
-        <v>0.45</v>
+        <v>0.4211</v>
       </c>
       <c r="L9" t="n">
         <v>0.625</v>
@@ -6287,28 +6288,28 @@
         <v>0.75</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5</v>
+        <v>0.4688</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.5278</v>
+        <v>0.4524</v>
       </c>
       <c r="R9" t="n">
         <v>0.8125</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6207</v>
+        <v>0.6071</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7922</v>
+        <v>0.7863</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6522</v>
+        <v>0.5833</v>
       </c>
       <c r="V9" t="n">
         <v>0.8478</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6765</v>
+        <v>0.6667</v>
       </c>
       <c r="X9" t="n">
         <v>0.3889</v>
@@ -6317,10 +6318,10 @@
         <v>0.7558</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.6857</v>
+        <v>0.6765</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.4</v>
+        <v>0.3684</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -6339,7 +6340,7 @@
         <v>0.9474</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5455</v>
+        <v>0.5</v>
       </c>
       <c r="E10" t="n">
         <v>0.5</v>
@@ -6348,13 +6349,13 @@
         <v>0.7941</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6705</v>
+        <v>0.6627999999999999</v>
       </c>
       <c r="H10" t="n">
         <v>0.9056999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7143</v>
+        <v>0.7059</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -6387,13 +6388,13 @@
         <v>0.8308</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6375</v>
+        <v>0.6282</v>
       </c>
       <c r="U10" t="n">
         <v>0.9583</v>
       </c>
       <c r="V10" t="n">
-        <v>0.82</v>
+        <v>0.8125</v>
       </c>
       <c r="W10" t="n">
         <v>0.9242</v>
@@ -6427,7 +6428,7 @@
         <v>0.9375</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6875</v>
+        <v>0.6111</v>
       </c>
       <c r="E11" t="n">
         <v>0.6667</v>
@@ -6436,13 +6437,13 @@
         <v>0.8333</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6852</v>
+        <v>0.6731</v>
       </c>
       <c r="H11" t="n">
         <v>0.9737</v>
       </c>
       <c r="I11" t="n">
-        <v>0.45</v>
+        <v>0.4211</v>
       </c>
       <c r="J11" t="n">
         <v>0.8962</v>
@@ -6475,13 +6476,13 @@
         <v>0.8625</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5</v>
+        <v>0.4773</v>
       </c>
       <c r="U11" t="n">
         <v>0.8125</v>
       </c>
       <c r="V11" t="n">
-        <v>0.75</v>
+        <v>0.7353</v>
       </c>
       <c r="W11" t="n">
         <v>0.9298</v>
@@ -6642,7 +6643,7 @@
         <v>0.625</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.2727</v>
+        <v>0.1667</v>
       </c>
       <c r="R13" t="n">
         <v>0.5</v>
@@ -6651,10 +6652,10 @@
         <v>0.8043</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7826</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.8333</v>
+        <v>0.7609</v>
       </c>
       <c r="V13" t="n">
         <v>0.7931</v>
@@ -6876,13 +6877,13 @@
         <v>0.7083</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5385</v>
+        <v>0.52</v>
       </c>
       <c r="H16" t="n">
         <v>0.8621</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5</v>
+        <v>0.4688</v>
       </c>
       <c r="J16" t="n">
         <v>0.8404</v>
@@ -6915,13 +6916,13 @@
         <v>0.8139999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4808</v>
+        <v>0.46</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
       </c>
       <c r="V16" t="n">
-        <v>0.8</v>
+        <v>0.7857</v>
       </c>
       <c r="W16" t="n">
         <v>0.8511</v>
@@ -6964,13 +6965,13 @@
         <v>0.7368</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5714</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="H17" t="n">
         <v>0.8</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5278</v>
+        <v>0.4524</v>
       </c>
       <c r="J17" t="n">
         <v>0.8462</v>
@@ -6982,7 +6983,7 @@
         <v>0.6667</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2727</v>
+        <v>0.1667</v>
       </c>
       <c r="N17" t="n">
         <v>0.8125</v>
@@ -7003,13 +7004,13 @@
         <v>0.75</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4773</v>
+        <v>0.3958</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5</v>
+        <v>0.4444</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5238</v>
+        <v>0.4783</v>
       </c>
       <c r="W17" t="n">
         <v>0.8</v>
@@ -7018,7 +7019,7 @@
         <v>0.75</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.4706</v>
+        <v>0.4444</v>
       </c>
       <c r="Z17" t="n">
         <v>0.75</v>
@@ -7131,7 +7132,7 @@
         <v>0.775</v>
       </c>
       <c r="D19" t="n">
-        <v>0.65</v>
+        <v>0.5909</v>
       </c>
       <c r="E19" t="n">
         <v>0.5</v>
@@ -7140,13 +7141,13 @@
         <v>0.8125</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6857</v>
+        <v>0.6765</v>
       </c>
       <c r="H19" t="n">
         <v>0.8718</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6207</v>
+        <v>0.6071</v>
       </c>
       <c r="J19" t="n">
         <v>0.8308</v>
@@ -7179,13 +7180,13 @@
         <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.6216</v>
       </c>
       <c r="U19" t="n">
         <v>0.8125</v>
       </c>
       <c r="V19" t="n">
-        <v>0.8448</v>
+        <v>0.8393</v>
       </c>
       <c r="W19" t="n">
         <v>0.8456</v>
@@ -7228,25 +7229,25 @@
         <v>0.6786</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7255</v>
+        <v>0.7157</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5227000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7922</v>
+        <v>0.7863</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6375</v>
+        <v>0.6282</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5</v>
+        <v>0.4773</v>
       </c>
       <c r="L20" t="n">
         <v>0.4688</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7826</v>
+        <v>0.7717000000000001</v>
       </c>
       <c r="N20" t="n">
         <v>0.5862000000000001</v>
@@ -7255,28 +7256,28 @@
         <v>0.5</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4808</v>
+        <v>0.46</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.4773</v>
+        <v>0.3958</v>
       </c>
       <c r="R20" t="n">
         <v>0.5625</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.6216</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5556</v>
+        <v>0.5</v>
       </c>
       <c r="V20" t="n">
-        <v>0.82</v>
+        <v>0.8133</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6477000000000001</v>
+        <v>0.6395</v>
       </c>
       <c r="X20" t="n">
         <v>0.5417</v>
@@ -7285,10 +7286,10 @@
         <v>0.7941</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.5795</v>
+        <v>0.5698</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.413</v>
+        <v>0.3864</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -7316,13 +7317,13 @@
         <v>0.75</v>
       </c>
       <c r="G21" t="n">
-        <v>0.675</v>
+        <v>0.5952</v>
       </c>
       <c r="H21" t="n">
         <v>0.875</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6522</v>
+        <v>0.5833</v>
       </c>
       <c r="J21" t="n">
         <v>0.9583</v>
@@ -7334,7 +7335,7 @@
         <v>0.5</v>
       </c>
       <c r="M21" t="n">
-        <v>0.8333</v>
+        <v>0.7609</v>
       </c>
       <c r="N21" t="n">
         <v>1</v>
@@ -7346,7 +7347,7 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.5</v>
+        <v>0.4444</v>
       </c>
       <c r="R21" t="n">
         <v>0.5</v>
@@ -7355,13 +7356,13 @@
         <v>0.8125</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5556</v>
+        <v>0.5</v>
       </c>
       <c r="U21" t="n">
         <v>1</v>
       </c>
       <c r="V21" t="n">
-        <v>0.7632</v>
+        <v>0.675</v>
       </c>
       <c r="W21" t="n">
         <v>0.9545</v>
@@ -7370,7 +7371,7 @@
         <v>1</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.6579</v>
+        <v>0.5952</v>
       </c>
       <c r="Z21" t="n">
         <v>0.9545</v>
@@ -7407,16 +7408,16 @@
         <v>0.859</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7647</v>
+        <v>0.75</v>
       </c>
       <c r="I22" t="n">
         <v>0.8478</v>
       </c>
       <c r="J22" t="n">
-        <v>0.82</v>
+        <v>0.8125</v>
       </c>
       <c r="K22" t="n">
-        <v>0.75</v>
+        <v>0.7353</v>
       </c>
       <c r="L22" t="n">
         <v>0.8</v>
@@ -7431,28 +7432,28 @@
         <v>0.8333</v>
       </c>
       <c r="P22" t="n">
-        <v>0.8</v>
+        <v>0.7857</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.5238</v>
+        <v>0.4783</v>
       </c>
       <c r="R22" t="n">
         <v>0.875</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8448</v>
+        <v>0.8393</v>
       </c>
       <c r="T22" t="n">
-        <v>0.82</v>
+        <v>0.8133</v>
       </c>
       <c r="U22" t="n">
-        <v>0.7632</v>
+        <v>0.675</v>
       </c>
       <c r="V22" t="n">
         <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>0.7759</v>
+        <v>0.7679</v>
       </c>
       <c r="X22" t="n">
         <v>1</v>
@@ -7461,10 +7462,10 @@
         <v>0.9048</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.7353</v>
+        <v>0.7188</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -7483,7 +7484,7 @@
         <v>0.9</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5909</v>
+        <v>0.5417</v>
       </c>
       <c r="E23" t="n">
         <v>0.5</v>
@@ -7492,13 +7493,13 @@
         <v>0.75</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7</v>
+        <v>0.6932</v>
       </c>
       <c r="H23" t="n">
         <v>0.9560999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6765</v>
+        <v>0.6667</v>
       </c>
       <c r="J23" t="n">
         <v>0.9242</v>
@@ -7531,13 +7532,13 @@
         <v>0.8456</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6477000000000001</v>
+        <v>0.6395</v>
       </c>
       <c r="U23" t="n">
         <v>0.9545</v>
       </c>
       <c r="V23" t="n">
-        <v>0.7759</v>
+        <v>0.7679</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
@@ -7698,7 +7699,7 @@
         <v>0.5625</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.4706</v>
+        <v>0.4444</v>
       </c>
       <c r="R25" t="n">
         <v>0.8889</v>
@@ -7710,7 +7711,7 @@
         <v>0.7941</v>
       </c>
       <c r="U25" t="n">
-        <v>0.6579</v>
+        <v>0.5952</v>
       </c>
       <c r="V25" t="n">
         <v>0.9048</v>
@@ -7747,7 +7748,7 @@
         <v>0.8158</v>
       </c>
       <c r="D26" t="n">
-        <v>0.35</v>
+        <v>0.3182</v>
       </c>
       <c r="E26" t="n">
         <v>0.5</v>
@@ -7756,13 +7757,13 @@
         <v>0.65</v>
       </c>
       <c r="G26" t="n">
-        <v>0.6932</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="H26" t="n">
         <v>0.8462</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6857</v>
+        <v>0.6765</v>
       </c>
       <c r="J26" t="n">
         <v>0.8646</v>
@@ -7795,13 +7796,13 @@
         <v>0.791</v>
       </c>
       <c r="T26" t="n">
-        <v>0.5795</v>
+        <v>0.5698</v>
       </c>
       <c r="U26" t="n">
         <v>0.9545</v>
       </c>
       <c r="V26" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.75</v>
       </c>
       <c r="W26" t="n">
         <v>0.8827</v>
@@ -7835,7 +7836,7 @@
         <v>0.8667</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="E27" t="n">
         <v>0.6667</v>
@@ -7844,13 +7845,13 @@
         <v>0.8333</v>
       </c>
       <c r="G27" t="n">
-        <v>0.68</v>
+        <v>0.6667</v>
       </c>
       <c r="H27" t="n">
         <v>0.9352</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4</v>
+        <v>0.3684</v>
       </c>
       <c r="J27" t="n">
         <v>0.8611</v>
@@ -7883,13 +7884,13 @@
         <v>0.8125</v>
       </c>
       <c r="T27" t="n">
-        <v>0.413</v>
+        <v>0.3864</v>
       </c>
       <c r="U27" t="n">
         <v>0.8125</v>
       </c>
       <c r="V27" t="n">
-        <v>0.7353</v>
+        <v>0.7188</v>
       </c>
       <c r="W27" t="n">
         <v>0.9298</v>
@@ -8156,6 +8157,2533 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.8626</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.4486</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.5481</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5818</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.8431</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.4713</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.7799</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.8315</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.5352</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.8024</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.6613</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.7534</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.5716</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.5813</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.3931</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.5359</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.7544</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.7671</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.4051</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Be95</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.8626</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.5078</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.8087</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6065</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.6853</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.8181</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.4985</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.7729</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.7992</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.6435</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.6066</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.7245</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.7258</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.7025</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.5229</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.6258</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.6552</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.4451</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.6096</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.5951</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.7383</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.8562</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.5273</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.7025</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.7158</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.4091</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>G. C</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.4486</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.5078</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8067</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4624</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.4514</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.5069</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.4645</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.4344</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.5072</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.4833</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.4713</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.4684</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.5767</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.5725</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.4888</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.5082</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.4043</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.5074</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.5328000000000001</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.4069</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>AynCDM16</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8087</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.8067</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.8025</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.6037</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6065</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.3718</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.4703</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.4767</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.6781</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.4019</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.8034</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.8267</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.8034</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.8034</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.8267</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.5424</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.4389</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.4702</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.8083</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.4702</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.4363</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.7333</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>AynCDM18</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.5481</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.6065</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.4624</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8025</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.4764</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5989</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.4662</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5152</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.6189</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.5674</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.4703</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.5026</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.6733</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.4567</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.4746</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.5471</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.5566</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.4236</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.5783</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.5165999999999999</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.5103</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.4652</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.5981</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.4025</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Mo417</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.5818</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.6853</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.4514</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.6037</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.4764</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.5155</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.4675</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.5051</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.5907</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.5198</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.4811</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.5039</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.4615</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.6194</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.5383</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.6577</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.4634</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.6498</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.4621</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.5075</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.4037</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>G. A</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.8431</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.8181</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.5069</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.6065</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.5989</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.5155</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.8038</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.9607</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5981</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.4537</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.7511</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.6543</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.7556</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.5785</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.6173999999999999</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.6613</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.3961</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.6133999999999999</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.4387</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.8407</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.4933</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.7761</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.902</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.4032</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>G. B</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.4713</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.4985</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.4645</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.3718</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4662</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.4336</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.4126</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.5443</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.6452</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.5185</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.6525</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.4668</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.4995</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.6492</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.4794</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.7467</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.6157</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.7887</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.4116</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.4495</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.6589</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.4185</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.3998</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.2701</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>CaH156</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.7799</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.7729</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.4344</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.4703</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5152</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.4675</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.8038</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.4336</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.8146</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.4515</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.4543</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.7433999999999999</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.5548</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.7988</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.5707</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.5199</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.6632</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.4077</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.5518</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.4499</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.9114</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.7883</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.4779</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.8745000000000001</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.7808</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.4018</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>CaH160</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.8315</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.7992</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.5072</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.4767</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.6189</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.9607</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.4126</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.8146</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.5984</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.4704</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.6176</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.757</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.5787</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.5923</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.6546999999999999</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.3811</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.5608</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.4279</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.8444</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.7914</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.5135999999999999</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.9286</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.4067</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>StPS26</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.5352</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.6435</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.4833</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.6781</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.5674</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.5051</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.5981</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.5443</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.4515</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.5984</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.4875</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.4666</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.7534</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.4487</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.5286</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.6807</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.4907</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.4655</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.5283</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.6188</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.6214</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.5889</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0.4149</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.5835</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.4784</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>TelK104</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6066</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.4713</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.4019</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.4703</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.5907</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.4537</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.6452</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.4543</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.4704</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.4875</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.6718</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.5605</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.4211</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.4704</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.6113</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.6021</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.5889</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.4738</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.4665</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.5847</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0.4527</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.4369</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Vi7</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.8024</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.7245</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.4684</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.8034</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.5026</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.5198</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.7511</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.5185</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.7433999999999999</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.4666</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.5901999999999999</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.7395</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.6151</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.6798</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.4094</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.6382</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.5096000000000001</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.7741</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.7823</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0.7425</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0.7085</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.4035</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>NH3</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.6613</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7258</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.5767</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8267</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.6733</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.6543</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.6525</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.5548</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.6176</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.7534</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.6718</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.5901999999999999</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.6756</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.5422</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.7447</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.5397</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.7105</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.6866</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.6118</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.6848</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.7188</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0.6118</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0.5886</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.6286</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Bi583</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.7534</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.7025</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.8034</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.4567</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.7556</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.4668</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.7988</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.757</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.4487</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.5605</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.7395</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.6756</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.5951</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.6121</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.6987</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.4044</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.5197000000000001</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0.7691</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.4519</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0.6888</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.6938</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.4035</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Ev1</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.5716</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5229</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.5725</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8034</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.4746</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.4811</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.5785</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.4995</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.5707</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.5787</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.5286</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.4211</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.5422</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.5951</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.6185</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.5199</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.4736</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.4906</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.4995</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.5891999999999999</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.4972</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0.4856</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.5675</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.4034</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>StP4 (IOM)</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.5813</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.6258</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.8267</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.5471</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.5039</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.6173999999999999</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.6492</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.5199</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.5923</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.6807</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.6151</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.6121</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.6185</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.5654</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.5464</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.6105</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.6753</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0.5546</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.6437</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0.5768</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.5513</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.6286</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Ye72a</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.6552</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.4888</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.5566</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.4615</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.6613</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.4794</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.6632</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.6546999999999999</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.4907</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.4704</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.6798</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.7447</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.6987</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.5199</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.5654</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.4302</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.6019</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.5407</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.6751</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.7129</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.5067</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.6609</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.6202</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.402</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>StPSnd104</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.3931</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4451</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.5082</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.4236</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.6194</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.3961</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.7467</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.4077</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.3811</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.4655</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.6113</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.4094</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.5397</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.4044</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.5464</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.4302</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.5334</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.7341</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.3974</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.4779</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.6419</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.2694</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>LoA16</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.6096</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.4043</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.5424</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.5783</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.5383</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.6133999999999999</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.6157</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.5518</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.5608</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.5283</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.6021</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.6382</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.7105</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.677</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.4736</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.6105</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.6019</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.5334</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.5819</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.5617</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.7095</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.5992</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0.5617</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.5383</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.4061</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Pa425</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.5951</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.4389</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.5165999999999999</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.6577</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.4387</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.7887</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.4499</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.4279</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.6188</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.5889</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.5096000000000001</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.6866</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.5197000000000001</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.4906</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.6753</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.5407</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.7341</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.5819</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.4397</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.5986</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.6714</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0.4384</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.4417</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.2704</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>NY2941/2</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.7383</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.3893</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.4702</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.5103</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.4634</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.8407</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.4116</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.9114</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.8444</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.4738</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.7741</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.6118</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.7691</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.4995</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.5546</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.6751</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.3974</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.5617</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.4397</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.4691</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0.8817</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.8151</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0.4018</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Pr2</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8562</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.5074</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.8083</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.5965</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.8120000000000001</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.4495</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.7883</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.7914</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.6214</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.4665</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.7823</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.6848</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.5891999999999999</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.7129</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.4779</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.7095</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.5986</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0.8159999999999999</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0.7423</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.7401</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0.4087</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>MosRSL78</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.5359</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.5273</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.5328000000000001</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.6498</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.4933</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.6589</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.4779</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.5135999999999999</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.5889</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.5847</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.7188</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.4519</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.4972</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.6437</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.5067</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.6419</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.5992</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.6714</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.4691</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0.4535</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.5026</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0.6051</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>NY2941/3</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.7544</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7025</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.4702</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.4652</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.4621</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.7761</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.4185</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.8745000000000001</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.4149</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.4527</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.7425</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.6118</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.6888</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.4856</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.5768</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.6609</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.5617</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.4384</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.8817</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0.7423</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.4535</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.7748</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0.4018</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Lo6673</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.7671</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7158</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.4363</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.5981</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.5075</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.902</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.3998</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.7808</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.9286</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.5835</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.4369</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.7085</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.5886</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.6938</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.5675</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.5513</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.6202</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.5383</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.4417</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0.8151</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.7401</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.5026</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0.7748</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0.4731</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>StPS1</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.4051</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.4091</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.4069</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.7333</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.4037</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.4032</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.2701</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.4067</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.4784</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.6286</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.4035</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.4034</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.6286</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.402</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.2694</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.4061</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.2704</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.4087</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0.6051</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.4731</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AB28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Be553</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Be95</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>G. C</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>AynCDM16</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>AynCDM18</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Mo417</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>G. A</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>G. B</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>CaH156</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>CaH160</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>StPS26</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>TelK104</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Vi7</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>NH3</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Bi583</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Ev1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>StP4 (IOM)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Ye72a</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>StPSnd104</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>LoA16</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Pa425</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>NY2941/2</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Pr2</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>MosRSL78</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>NY2941/3</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Lo6673</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>StPS1</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Be553</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
@@ -8189,7 +10717,7 @@
         <v>0.4648</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5048</v>
+        <v>0.505</v>
       </c>
       <c r="N2" t="n">
         <v>0.1976</v>
@@ -8201,7 +10729,7 @@
         <v>0.2466</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.429</v>
+        <v>0.4284</v>
       </c>
       <c r="R2" t="n">
         <v>0.4187</v>
@@ -8210,7 +10738,7 @@
         <v>0.284</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6071</v>
+        <v>0.6069</v>
       </c>
       <c r="U2" t="n">
         <v>0.3333</v>
@@ -8289,7 +10817,7 @@
         <v>0.2975</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4778</v>
+        <v>0.4771</v>
       </c>
       <c r="R3" t="n">
         <v>0.3742</v>
@@ -8298,7 +10826,7 @@
         <v>0.3448</v>
       </c>
       <c r="T3" t="n">
-        <v>0.555</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="U3" t="n">
         <v>0.3904</v>
@@ -8350,16 +10878,16 @@
         <v>0.5486</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4386</v>
+        <v>0.4931</v>
       </c>
       <c r="I4" t="n">
         <v>0.5355</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5312</v>
+        <v>0.5656</v>
       </c>
       <c r="K4" t="n">
-        <v>0.4383</v>
+        <v>0.4928</v>
       </c>
       <c r="L4" t="n">
         <v>0.5167</v>
@@ -8377,16 +10905,16 @@
         <v>0.493</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4278</v>
+        <v>0.4275</v>
       </c>
       <c r="R4" t="n">
         <v>0.6513</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5046</v>
+        <v>0.5112</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4919</v>
+        <v>0.4918</v>
       </c>
       <c r="U4" t="n">
         <v>0.5957</v>
@@ -8395,7 +10923,7 @@
         <v>0.699</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5799</v>
+        <v>0.6107</v>
       </c>
       <c r="X4" t="n">
         <v>0.4926</v>
@@ -8404,10 +10932,10 @@
         <v>0.4672</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.6264</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.5768</v>
       </c>
       <c r="AB4" t="n">
         <v>0.5931</v>
@@ -8465,7 +10993,7 @@
         <v>0.1966</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1967</v>
+        <v>0.1966</v>
       </c>
       <c r="R5" t="n">
         <v>0.1733</v>
@@ -8541,7 +11069,7 @@
         <v>0.4326</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5296</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="N6" t="n">
         <v>0.4974</v>
@@ -8553,7 +11081,7 @@
         <v>0.5433</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.526</v>
+        <v>0.5254</v>
       </c>
       <c r="R6" t="n">
         <v>0.4529</v>
@@ -8562,7 +11090,7 @@
         <v>0.4434</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5766</v>
+        <v>0.5764</v>
       </c>
       <c r="U6" t="n">
         <v>0.4217</v>
@@ -8614,13 +11142,13 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4853</v>
+        <v>0.4845</v>
       </c>
       <c r="I7" t="n">
         <v>0.364</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5312</v>
+        <v>0.5325</v>
       </c>
       <c r="K7" t="n">
         <v>0.501</v>
@@ -8629,7 +11157,7 @@
         <v>0.4949</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4091</v>
+        <v>0.4093</v>
       </c>
       <c r="N7" t="n">
         <v>0.4802</v>
@@ -8638,28 +11166,28 @@
         <v>0.473</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5777</v>
+        <v>0.58</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5165999999999999</v>
+        <v>0.5189</v>
       </c>
       <c r="R7" t="n">
         <v>0.4961</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5374</v>
+        <v>0.5385</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3769</v>
+        <v>0.3806</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4374</v>
+        <v>0.4617</v>
       </c>
       <c r="V7" t="n">
         <v>0.3423</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5352</v>
+        <v>0.5366</v>
       </c>
       <c r="X7" t="n">
         <v>0.313</v>
@@ -8668,10 +11196,10 @@
         <v>0.3502</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.5366</v>
+        <v>0.5379</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.4935</v>
+        <v>0.4925</v>
       </c>
       <c r="AB7" t="n">
         <v>0.5963000000000001</v>
@@ -8690,7 +11218,7 @@
         <v>0.1819</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4386</v>
+        <v>0.4931</v>
       </c>
       <c r="E8" t="n">
         <v>0.3935</v>
@@ -8699,13 +11227,13 @@
         <v>0.4011</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4853</v>
+        <v>0.4845</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>0.594</v>
+        <v>0.597</v>
       </c>
       <c r="J8" t="n">
         <v>0.1962</v>
@@ -8717,7 +11245,7 @@
         <v>0.4019</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5576</v>
+        <v>0.5463</v>
       </c>
       <c r="N8" t="n">
         <v>0.2489</v>
@@ -8729,7 +11257,7 @@
         <v>0.2444</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4218</v>
+        <v>0.4215</v>
       </c>
       <c r="R8" t="n">
         <v>0.3826</v>
@@ -8738,13 +11266,13 @@
         <v>0.3387</v>
       </c>
       <c r="T8" t="n">
-        <v>0.601</v>
+        <v>0.6039</v>
       </c>
       <c r="U8" t="n">
         <v>0.3866</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5383</v>
+        <v>0.5613</v>
       </c>
       <c r="W8" t="n">
         <v>0.1593</v>
@@ -8790,22 +11318,22 @@
         <v>0.364</v>
       </c>
       <c r="H9" t="n">
-        <v>0.594</v>
+        <v>0.597</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5648</v>
+        <v>0.5664</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5848</v>
+        <v>0.5874</v>
       </c>
       <c r="L9" t="n">
         <v>0.4557</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3606</v>
+        <v>0.3548</v>
       </c>
       <c r="N9" t="n">
         <v>0.4815</v>
@@ -8814,28 +11342,28 @@
         <v>0.3475</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5336</v>
+        <v>0.5332</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4712</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="R9" t="n">
         <v>0.3508</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5204</v>
+        <v>0.5206</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2476</v>
+        <v>0.2533</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3602</v>
+        <v>0.3843</v>
       </c>
       <c r="V9" t="n">
         <v>0.2113</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5863</v>
+        <v>0.5884</v>
       </c>
       <c r="X9" t="n">
         <v>0.5505</v>
@@ -8844,10 +11372,10 @@
         <v>0.3411</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.5794</v>
+        <v>0.5815</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.5965</v>
+        <v>0.6002</v>
       </c>
       <c r="AB9" t="n">
         <v>0.7299</v>
@@ -8866,7 +11394,7 @@
         <v>0.2271</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5312</v>
+        <v>0.5656</v>
       </c>
       <c r="E10" t="n">
         <v>0.5296999999999999</v>
@@ -8875,13 +11403,13 @@
         <v>0.4848</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5312</v>
+        <v>0.5325</v>
       </c>
       <c r="H10" t="n">
         <v>0.1962</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5648</v>
+        <v>0.5664</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -8893,7 +11421,7 @@
         <v>0.5485</v>
       </c>
       <c r="M10" t="n">
-        <v>0.549</v>
+        <v>0.5457</v>
       </c>
       <c r="N10" t="n">
         <v>0.2566</v>
@@ -8905,7 +11433,7 @@
         <v>0.2012</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4295</v>
+        <v>0.4293</v>
       </c>
       <c r="R10" t="n">
         <v>0.4801</v>
@@ -8914,13 +11442,13 @@
         <v>0.3368</v>
       </c>
       <c r="T10" t="n">
-        <v>0.5905</v>
+        <v>0.5923</v>
       </c>
       <c r="U10" t="n">
         <v>0.4482</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5494</v>
+        <v>0.5501</v>
       </c>
       <c r="W10" t="n">
         <v>0.0886</v>
@@ -8954,7 +11482,7 @@
         <v>0.2008</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4383</v>
+        <v>0.4928</v>
       </c>
       <c r="E11" t="n">
         <v>0.5233</v>
@@ -8969,7 +11497,7 @@
         <v>0.0393</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5848</v>
+        <v>0.5874</v>
       </c>
       <c r="J11" t="n">
         <v>0.1854</v>
@@ -8981,7 +11509,7 @@
         <v>0.4016</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5409</v>
+        <v>0.5296</v>
       </c>
       <c r="N11" t="n">
         <v>0.27</v>
@@ -8993,7 +11521,7 @@
         <v>0.243</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4217</v>
+        <v>0.4213</v>
       </c>
       <c r="R11" t="n">
         <v>0.4077</v>
@@ -9002,13 +11530,13 @@
         <v>0.3453</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.6189</v>
       </c>
       <c r="U11" t="n">
         <v>0.4392</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5495</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="W11" t="n">
         <v>0.1556</v>
@@ -9081,7 +11609,7 @@
         <v>0.5513</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.4719</v>
+        <v>0.4714</v>
       </c>
       <c r="R12" t="n">
         <v>0.3193</v>
@@ -9090,7 +11618,7 @@
         <v>0.5093</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5346</v>
+        <v>0.5345</v>
       </c>
       <c r="U12" t="n">
         <v>0.4717</v>
@@ -9124,7 +11652,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5048</v>
+        <v>0.505</v>
       </c>
       <c r="C13" t="n">
         <v>0.3934</v>
@@ -9136,22 +11664,22 @@
         <v>0.5981</v>
       </c>
       <c r="F13" t="n">
+        <v>0.5296999999999999</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.4093</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.5463</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.5457</v>
+      </c>
+      <c r="K13" t="n">
         <v>0.5296</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.4091</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.5576</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.3606</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.549</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.5409</v>
       </c>
       <c r="L13" t="n">
         <v>0.5125</v>
@@ -9160,46 +11688,46 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5189</v>
+        <v>0.519</v>
       </c>
       <c r="O13" t="n">
-        <v>0.3281</v>
+        <v>0.3282</v>
       </c>
       <c r="P13" t="n">
-        <v>0.4728</v>
+        <v>0.4395</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.5431</v>
+        <v>0.5789</v>
       </c>
       <c r="R13" t="n">
         <v>0.393</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5295</v>
+        <v>0.5296</v>
       </c>
       <c r="T13" t="n">
-        <v>0.3897</v>
+        <v>0.3887</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3658</v>
+        <v>0.3979</v>
       </c>
       <c r="V13" t="n">
-        <v>0.4186</v>
+        <v>0.4111</v>
       </c>
       <c r="W13" t="n">
-        <v>0.5301</v>
+        <v>0.5262</v>
       </c>
       <c r="X13" t="n">
-        <v>0.5334</v>
+        <v>0.5335</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.4151</v>
+        <v>0.4153</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.5471</v>
+        <v>0.5473</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.5744</v>
+        <v>0.5631</v>
       </c>
       <c r="AB13" t="n">
         <v>1</v>
@@ -9245,7 +11773,7 @@
         <v>0.5334</v>
       </c>
       <c r="M14" t="n">
-        <v>0.5189</v>
+        <v>0.519</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -9257,7 +11785,7 @@
         <v>0.2605</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.4427</v>
+        <v>0.442</v>
       </c>
       <c r="R14" t="n">
         <v>0.3849</v>
@@ -9266,7 +11794,7 @@
         <v>0.3202</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5908</v>
+        <v>0.5906</v>
       </c>
       <c r="U14" t="n">
         <v>0.3618</v>
@@ -9333,7 +11861,7 @@
         <v>0.2466</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3281</v>
+        <v>0.3282</v>
       </c>
       <c r="N15" t="n">
         <v>0.4098</v>
@@ -9345,7 +11873,7 @@
         <v>0.3244</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.4581</v>
+        <v>0.4578</v>
       </c>
       <c r="R15" t="n">
         <v>0.22</v>
@@ -9354,7 +11882,7 @@
         <v>0.2553</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4604</v>
+        <v>0.4603</v>
       </c>
       <c r="U15" t="n">
         <v>0.2895</v>
@@ -9403,13 +11931,13 @@
         <v>0.5433</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5777</v>
+        <v>0.58</v>
       </c>
       <c r="H16" t="n">
         <v>0.2444</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5336</v>
+        <v>0.5332</v>
       </c>
       <c r="J16" t="n">
         <v>0.2012</v>
@@ -9421,7 +11949,7 @@
         <v>0.5513</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4728</v>
+        <v>0.4395</v>
       </c>
       <c r="N16" t="n">
         <v>0.2605</v>
@@ -9433,7 +11961,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.4052</v>
+        <v>0.4049</v>
       </c>
       <c r="R16" t="n">
         <v>0.3879</v>
@@ -9442,13 +11970,13 @@
         <v>0.3013</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5931</v>
+        <v>0.5956</v>
       </c>
       <c r="U16" t="n">
         <v>0.323</v>
       </c>
       <c r="V16" t="n">
-        <v>0.4847</v>
+        <v>0.4803</v>
       </c>
       <c r="W16" t="n">
         <v>0.2309</v>
@@ -9476,85 +12004,85 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.429</v>
+        <v>0.4284</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4778</v>
+        <v>0.4771</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4278</v>
+        <v>0.4275</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1967</v>
+        <v>0.1966</v>
       </c>
       <c r="F17" t="n">
-        <v>0.526</v>
+        <v>0.5254</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5165999999999999</v>
+        <v>0.5189</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4218</v>
+        <v>0.4215</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4712</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4295</v>
+        <v>0.4293</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4217</v>
+        <v>0.4213</v>
       </c>
       <c r="L17" t="n">
-        <v>0.4719</v>
+        <v>0.4714</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5431</v>
+        <v>0.5789</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4427</v>
+        <v>0.442</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4581</v>
+        <v>0.4578</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4052</v>
+        <v>0.4049</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3821</v>
+        <v>0.3815</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4804</v>
+        <v>0.4801</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5769</v>
+        <v>0.5999</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5281</v>
+        <v>0.5264</v>
       </c>
       <c r="V17" t="n">
-        <v>0.507</v>
+        <v>0.5094</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5008</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="X17" t="n">
-        <v>0.4114</v>
+        <v>0.4108</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.5013</v>
+        <v>0.5028</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.5144</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.4328</v>
+        <v>0.4325</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.5967</v>
+        <v>0.5966</v>
       </c>
     </row>
     <row r="18">
@@ -9609,7 +12137,7 @@
         <v>0.3879</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.3821</v>
+        <v>0.3815</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -9658,7 +12186,7 @@
         <v>0.3448</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5046</v>
+        <v>0.5112</v>
       </c>
       <c r="E19" t="n">
         <v>0.596</v>
@@ -9667,13 +12195,13 @@
         <v>0.4434</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5374</v>
+        <v>0.5385</v>
       </c>
       <c r="H19" t="n">
         <v>0.3387</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5204</v>
+        <v>0.5206</v>
       </c>
       <c r="J19" t="n">
         <v>0.3368</v>
@@ -9685,7 +12213,7 @@
         <v>0.5093</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5295</v>
+        <v>0.5296</v>
       </c>
       <c r="N19" t="n">
         <v>0.3202</v>
@@ -9697,7 +12225,7 @@
         <v>0.3013</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.4804</v>
+        <v>0.4801</v>
       </c>
       <c r="R19" t="n">
         <v>0.4346</v>
@@ -9706,13 +12234,13 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5683</v>
+        <v>0.5698</v>
       </c>
       <c r="U19" t="n">
         <v>0.3981</v>
       </c>
       <c r="V19" t="n">
-        <v>0.4485</v>
+        <v>0.4593</v>
       </c>
       <c r="W19" t="n">
         <v>0.3249</v>
@@ -9740,85 +12268,85 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6071</v>
+        <v>0.6069</v>
       </c>
       <c r="C20" t="n">
-        <v>0.555</v>
+        <v>0.5548999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4919</v>
+        <v>0.4918</v>
       </c>
       <c r="E20" t="n">
         <v>0.6293</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5766</v>
+        <v>0.5764</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3769</v>
+        <v>0.3806</v>
       </c>
       <c r="H20" t="n">
-        <v>0.601</v>
+        <v>0.6039</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2476</v>
+        <v>0.2533</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5905</v>
+        <v>0.5923</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6153999999999999</v>
+        <v>0.6189</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5346</v>
+        <v>0.5345</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3897</v>
+        <v>0.3887</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5908</v>
+        <v>0.5906</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4604</v>
+        <v>0.4603</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5931</v>
+        <v>0.5956</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.5769</v>
+        <v>0.5999</v>
       </c>
       <c r="R20" t="n">
         <v>0.4536</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5683</v>
+        <v>0.5698</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4492</v>
+        <v>0.4666</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2596</v>
+        <v>0.2659</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6005</v>
+        <v>0.6026</v>
       </c>
       <c r="X20" t="n">
-        <v>0.5222</v>
+        <v>0.5221</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.3584</v>
+        <v>0.3581</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.6318</v>
+        <v>0.6347</v>
       </c>
       <c r="AA20" t="n">
-        <v>0.6344</v>
+        <v>0.6388</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.7307</v>
+        <v>0.7306</v>
       </c>
     </row>
     <row r="21">
@@ -9843,13 +12371,13 @@
         <v>0.4217</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4374</v>
+        <v>0.4617</v>
       </c>
       <c r="H21" t="n">
         <v>0.3866</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3602</v>
+        <v>0.3843</v>
       </c>
       <c r="J21" t="n">
         <v>0.4482</v>
@@ -9861,7 +12389,7 @@
         <v>0.4717</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3658</v>
+        <v>0.3979</v>
       </c>
       <c r="N21" t="n">
         <v>0.3618</v>
@@ -9873,7 +12401,7 @@
         <v>0.323</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.5281</v>
+        <v>0.5264</v>
       </c>
       <c r="R21" t="n">
         <v>0.3895</v>
@@ -9882,13 +12410,13 @@
         <v>0.3981</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4492</v>
+        <v>0.4666</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3901</v>
+        <v>0.4181</v>
       </c>
       <c r="W21" t="n">
         <v>0.4383</v>
@@ -9897,7 +12425,7 @@
         <v>0.2905</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.3867</v>
+        <v>0.4008</v>
       </c>
       <c r="Z21" t="n">
         <v>0.4383</v>
@@ -9934,22 +12462,22 @@
         <v>0.3423</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5383</v>
+        <v>0.5613</v>
       </c>
       <c r="I22" t="n">
         <v>0.2113</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5494</v>
+        <v>0.5501</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5495</v>
+        <v>0.5721000000000001</v>
       </c>
       <c r="L22" t="n">
         <v>0.3812</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4186</v>
+        <v>0.4111</v>
       </c>
       <c r="N22" t="n">
         <v>0.4904</v>
@@ -9958,28 +12486,28 @@
         <v>0.3134</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4847</v>
+        <v>0.4803</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.507</v>
+        <v>0.5094</v>
       </c>
       <c r="R22" t="n">
         <v>0.3247</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4485</v>
+        <v>0.4593</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2596</v>
+        <v>0.2659</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3901</v>
+        <v>0.4181</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5591</v>
+        <v>0.5603</v>
       </c>
       <c r="X22" t="n">
         <v>0.4014</v>
@@ -9988,10 +12516,10 @@
         <v>0.3286</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.5601</v>
+        <v>0.5616</v>
       </c>
       <c r="AA22" t="n">
-        <v>0.5361</v>
+        <v>0.5583</v>
       </c>
       <c r="AB22" t="n">
         <v>0.7296</v>
@@ -10010,7 +12538,7 @@
         <v>0.2617</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5799</v>
+        <v>0.6107</v>
       </c>
       <c r="E23" t="n">
         <v>0.5298</v>
@@ -10019,13 +12547,13 @@
         <v>0.4897</v>
       </c>
       <c r="G23" t="n">
-        <v>0.5352</v>
+        <v>0.5366</v>
       </c>
       <c r="H23" t="n">
         <v>0.1593</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5863</v>
+        <v>0.5884</v>
       </c>
       <c r="J23" t="n">
         <v>0.0886</v>
@@ -10037,7 +12565,7 @@
         <v>0.537</v>
       </c>
       <c r="M23" t="n">
-        <v>0.5301</v>
+        <v>0.5262</v>
       </c>
       <c r="N23" t="n">
         <v>0.2259</v>
@@ -10049,7 +12577,7 @@
         <v>0.2309</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.5008</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="R23" t="n">
         <v>0.4454</v>
@@ -10058,13 +12586,13 @@
         <v>0.3249</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6005</v>
+        <v>0.6026</v>
       </c>
       <c r="U23" t="n">
         <v>0.4383</v>
       </c>
       <c r="V23" t="n">
-        <v>0.5591</v>
+        <v>0.5603</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
@@ -10125,7 +12653,7 @@
         <v>0.3786</v>
       </c>
       <c r="M24" t="n">
-        <v>0.5334</v>
+        <v>0.5335</v>
       </c>
       <c r="N24" t="n">
         <v>0.2177</v>
@@ -10137,7 +12665,7 @@
         <v>0.258</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.4114</v>
+        <v>0.4108</v>
       </c>
       <c r="R24" t="n">
         <v>0.515</v>
@@ -10146,7 +12674,7 @@
         <v>0.2871</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5222</v>
+        <v>0.5221</v>
       </c>
       <c r="U24" t="n">
         <v>0.2905</v>
@@ -10213,7 +12741,7 @@
         <v>0.4111</v>
       </c>
       <c r="M25" t="n">
-        <v>0.4151</v>
+        <v>0.4153</v>
       </c>
       <c r="N25" t="n">
         <v>0.51</v>
@@ -10225,7 +12753,7 @@
         <v>0.5481</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.5013</v>
+        <v>0.5028</v>
       </c>
       <c r="R25" t="n">
         <v>0.3563</v>
@@ -10234,10 +12762,10 @@
         <v>0.4933</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3584</v>
+        <v>0.3581</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3867</v>
+        <v>0.4008</v>
       </c>
       <c r="V25" t="n">
         <v>0.3286</v>
@@ -10274,7 +12802,7 @@
         <v>0.2975</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6264</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="E26" t="n">
         <v>0.5298</v>
@@ -10283,13 +12811,13 @@
         <v>0.5348000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5366</v>
+        <v>0.5379</v>
       </c>
       <c r="H26" t="n">
         <v>0.2239</v>
       </c>
       <c r="I26" t="n">
-        <v>0.5794</v>
+        <v>0.5815</v>
       </c>
       <c r="J26" t="n">
         <v>0.1255</v>
@@ -10301,7 +12829,7 @@
         <v>0.5851</v>
       </c>
       <c r="M26" t="n">
-        <v>0.5471</v>
+        <v>0.5473</v>
       </c>
       <c r="N26" t="n">
         <v>0.2575</v>
@@ -10313,7 +12841,7 @@
         <v>0.3112</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.5145999999999999</v>
+        <v>0.5144</v>
       </c>
       <c r="R26" t="n">
         <v>0.4232</v>
@@ -10322,13 +12850,13 @@
         <v>0.3391</v>
       </c>
       <c r="T26" t="n">
-        <v>0.6318</v>
+        <v>0.6347</v>
       </c>
       <c r="U26" t="n">
         <v>0.4383</v>
       </c>
       <c r="V26" t="n">
-        <v>0.5601</v>
+        <v>0.5616</v>
       </c>
       <c r="W26" t="n">
         <v>0.1183</v>
@@ -10362,7 +12890,7 @@
         <v>0.2842</v>
       </c>
       <c r="D27" t="n">
-        <v>0.5377999999999999</v>
+        <v>0.5768</v>
       </c>
       <c r="E27" t="n">
         <v>0.5637</v>
@@ -10371,13 +12899,13 @@
         <v>0.4019</v>
       </c>
       <c r="G27" t="n">
-        <v>0.4935</v>
+        <v>0.4925</v>
       </c>
       <c r="H27" t="n">
         <v>0.098</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5965</v>
+        <v>0.6002</v>
       </c>
       <c r="J27" t="n">
         <v>0.2192</v>
@@ -10389,7 +12917,7 @@
         <v>0.4165</v>
       </c>
       <c r="M27" t="n">
-        <v>0.5744</v>
+        <v>0.5631</v>
       </c>
       <c r="N27" t="n">
         <v>0.2915</v>
@@ -10401,7 +12929,7 @@
         <v>0.3062</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.4328</v>
+        <v>0.4325</v>
       </c>
       <c r="R27" t="n">
         <v>0.4487</v>
@@ -10410,13 +12938,13 @@
         <v>0.3798</v>
       </c>
       <c r="T27" t="n">
-        <v>0.6344</v>
+        <v>0.6388</v>
       </c>
       <c r="U27" t="n">
         <v>0.4617</v>
       </c>
       <c r="V27" t="n">
-        <v>0.5361</v>
+        <v>0.5583</v>
       </c>
       <c r="W27" t="n">
         <v>0.1849</v>
@@ -10489,7 +13017,7 @@
         <v>0.5965</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.5967</v>
+        <v>0.5966</v>
       </c>
       <c r="R28" t="n">
         <v>0.3714</v>
@@ -10498,7 +13026,7 @@
         <v>0.598</v>
       </c>
       <c r="T28" t="n">
-        <v>0.7307</v>
+        <v>0.7306</v>
       </c>
       <c r="U28" t="n">
         <v>0.5939</v>
